--- a/models/model_data/log/model accs.xlsx
+++ b/models/model_data/log/model accs.xlsx
@@ -1787,7 +1787,6 @@
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -2520,7 +2519,6 @@
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -2583,7 +2581,6 @@
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -3316,7 +3313,6 @@
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -3379,7 +3375,6 @@
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -4676,6 +4671,7 @@
           <t>100.0±0.00</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -4738,6 +4734,7 @@
           <t>100.0±0.00</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -6274,6 +6271,7 @@
           <t>100.0±0.00</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
@@ -6336,6 +6334,7 @@
           <t>100.0±0.00</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>100.0±0.00</t>

--- a/models/model_data/log/model accs.xlsx
+++ b/models/model_data/log/model accs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1038" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1038_province_data" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1040" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1040_province_data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,77 +519,77 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97.7±0.12</t>
+          <t>97.8±0.05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>95.4±0.96</t>
+          <t>96.3±0.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>96.0±0.29</t>
+          <t>96.7±0.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>97.7±0.13</t>
+          <t>97.8±0.05</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.961±0.00214</t>
+          <t>0.962±0.00092</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>80.4±1.28</t>
+          <t>81.4±1.06</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>96.6±0.47</t>
+          <t>96.3±0.55</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>98.7±0.32</t>
+          <t>98.8±0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>97.6±0.36</t>
+          <t>97.5±0.32</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>88.6±0.80</t>
+          <t>89.9±0.55</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>81.3±1.45</t>
+          <t>82.1±0.98</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>93.0±0.84</t>
+          <t>93.8±0.37</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>91.7±0.75</t>
+          <t>92.1±0.54</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>92.4±0.71</t>
+          <t>92.9±0.39</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>84.5±1.56</t>
+          <t>88.7±0.91</t>
         </is>
       </c>
     </row>
@@ -601,77 +601,77 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.7±0.04</t>
+          <t>97.8±0.07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>95.0±0.50</t>
+          <t>96.5±0.69</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>95.8±0.13</t>
+          <t>96.8±0.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>97.6±0.04</t>
+          <t>97.8±0.07</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.960±0.00074</t>
+          <t>0.963±0.00124</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>80.1±0.28</t>
+          <t>81.8±0.57</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>96.7±0.58</t>
+          <t>96.6±0.24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>98.7±0.32</t>
+          <t>98.7±0.24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>97.7±0.23</t>
+          <t>97.6±0.18</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>87.9±0.48</t>
+          <t>90.0±0.67</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>81.3±0.18</t>
+          <t>82.6±0.55</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>92.6±0.38</t>
+          <t>93.9±0.39</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>92.1±0.09</t>
+          <t>92.3±0.20</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>92.3±0.19</t>
+          <t>93.0±0.22</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>83.1±1.71</t>
+          <t>89.1±0.88</t>
         </is>
       </c>
     </row>
@@ -683,77 +683,77 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>96.7±0.22</t>
+          <t>96.9±0.21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>94.2±0.68</t>
+          <t>94.4±0.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>94.6±0.57</t>
+          <t>95.5±0.53</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>96.7±0.22</t>
+          <t>96.9±0.21</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.944±0.00371</t>
+          <t>0.946±0.00357</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>73.1±2.15</t>
+          <t>74.4±2.12</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>95.3±0.33</t>
+          <t>95.5±0.62</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>98.3±0.31</t>
+          <t>98.4±0.27</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.8±0.28</t>
+          <t>96.9±0.43</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>83.6±1.49</t>
+          <t>85.9±1.19</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>74.2±1.95</t>
+          <t>75.3±2.03</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>89.2±0.95</t>
+          <t>90.7±0.81</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>88.3±0.99</t>
+          <t>89.0±0.96</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>88.8±0.94</t>
+          <t>89.8±0.88</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>77.9±2.59</t>
+          <t>83.4±2.16</t>
         </is>
       </c>
     </row>
@@ -765,77 +765,77 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>96.8±0.10</t>
+          <t>97.0±0.13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>93.3±0.48</t>
+          <t>94.9±0.68</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>94.7±0.30</t>
+          <t>95.8±0.27</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>96.8±0.11</t>
+          <t>97.0±0.13</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.945±0.00183</t>
+          <t>0.949±0.00229</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>73.7±1.28</t>
+          <t>75.3±1.00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>95.8±0.30</t>
+          <t>95.8±0.67</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>98.6±0.20</t>
+          <t>98.4±0.40</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>97.2±0.23</t>
+          <t>97.1±0.47</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>84.0±0.85</t>
+          <t>86.2±0.69</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>74.4±1.30</t>
+          <t>76.1±0.91</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>89.0±0.34</t>
+          <t>90.8±0.51</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>88.4±0.82</t>
+          <t>89.5±0.54</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>88.7±0.55</t>
+          <t>90.2±0.45</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>77.9±1.84</t>
+          <t>84.2±1.36</t>
         </is>
       </c>
     </row>
@@ -847,77 +847,77 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>97.2±0.06</t>
+          <t>97.4±0.12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>93.9±0.77</t>
+          <t>95.8±0.41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>94.7±0.34</t>
+          <t>95.9±0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>97.2±0.06</t>
+          <t>97.4±0.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.952±0.00101</t>
+          <t>0.956±0.00202</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>77.1±1.01</t>
+          <t>78.5±1.26</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>95.7±0.60</t>
+          <t>95.6±0.49</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>98.7±0.18</t>
+          <t>98.5±0.55</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>97.2±0.40</t>
+          <t>97.1±0.47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>85.7±0.92</t>
+          <t>88.3±0.77</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>77.8±1.03</t>
+          <t>79.1±1.44</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>91.3±0.51</t>
+          <t>92.8±0.77</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>89.8±0.37</t>
+          <t>90.7±0.50</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>90.5±0.30</t>
+          <t>91.7±0.59</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>77.6±2.80</t>
+          <t>85.6±1.91</t>
         </is>
       </c>
     </row>
@@ -929,77 +929,77 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.4±0.05</t>
+          <t>97.5±0.08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>94.4±0.32</t>
+          <t>96.0±0.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>95.3±0.15</t>
+          <t>96.2±0.26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>97.4±0.05</t>
+          <t>97.5±0.08</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.955±0.00082</t>
+          <t>0.957±0.00144</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>77.2±1.17</t>
+          <t>78.9±1.35</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>95.9±0.61</t>
+          <t>95.9±0.47</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>98.7±0.08</t>
+          <t>98.6±0.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>97.3±0.31</t>
+          <t>97.2±0.28</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>85.7±0.65</t>
+          <t>87.9±0.67</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>77.5±1.21</t>
+          <t>79.2±1.35</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>91.7±0.45</t>
+          <t>93.1±0.74</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>90.0±0.46</t>
+          <t>90.7±0.49</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>90.8±0.45</t>
+          <t>91.9±0.57</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>79.3±1.37</t>
+          <t>84.8±2.17</t>
         </is>
       </c>
     </row>
@@ -1117,77 +1117,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>97.8±0.20</t>
+          <t>98.0±0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>91.1±3.95</t>
+          <t>91.8±2.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>90.4±1.18</t>
+          <t>92.0±1.03</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97.8±0.21</t>
+          <t>98.0±0.12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.954±0.00427</t>
+          <t>0.959±0.00242</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>76.5±1.96</t>
+          <t>79.9±1.48</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>99.6±0.39</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>99.0±0.30</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>99.3±0.22</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>93.3±0.62</t>
+          <t>93.6±0.60</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>76.6±1.92</t>
+          <t>79.9±1.48</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>93.4±0.97</t>
+          <t>94.6±0.45</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>92.9±0.48</t>
+          <t>94.5±0.41</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>93.1±0.67</t>
+          <t>94.5±0.39</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>82.8±3.01</t>
+          <t>88.8±1.58</t>
         </is>
       </c>
     </row>
@@ -1204,77 +1204,77 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>97.8±0.08</t>
+          <t>98.0±0.11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>93.8±1.81</t>
+          <t>94.4±1.10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>92.1±1.31</t>
+          <t>93.3±0.38</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>97.8±0.09</t>
+          <t>98.0±0.11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.955±0.00179</t>
+          <t>0.959±0.00219</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>76.2±1.78</t>
+          <t>80.9±1.52</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>99.5±0.41</t>
+          <t>100.0±0.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>98.8±0.40</t>
+          <t>99.7±0.54</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>99.2±0.34</t>
+          <t>99.9±0.29</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>93.2±1.19</t>
+          <t>93.9±0.53</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>76.3±1.80</t>
+          <t>80.9±1.52</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>93.1±0.64</t>
+          <t>95.0±0.54</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>93.0±0.51</t>
+          <t>94.7±0.46</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>93.1±0.55</t>
+          <t>94.9±0.44</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>87.3±3.33</t>
+          <t>92.2±1.02</t>
         </is>
       </c>
     </row>
@@ -1291,77 +1291,77 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>99.3±0.05</t>
+          <t>99.0±0.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>97.5±0.57</t>
+          <t>99.0±0.10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>97.7±0.12</t>
+          <t>96.8±1.32</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>99.3±0.05</t>
+          <t>99.0±0.09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.989±0.00083</t>
+          <t>0.983±0.00169</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>93.9±0.85</t>
+          <t>92.4±0.77</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>99.8±0.08</t>
+          <t>98.1±0.30</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>99.9±0.04</t>
+          <t>99.0±0.15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.9±0.06</t>
+          <t>98.5±0.22</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>95.2±0.82</t>
+          <t>92.8±1.31</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>94.6±0.86</t>
+          <t>92.9±0.58</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>97.9±0.46</t>
+          <t>97.9±0.36</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>96.7±0.49</t>
+          <t>96.0±0.59</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>97.3±0.39</t>
+          <t>96.9±0.39</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>90.3±1.81</t>
+          <t>86.1±6.10</t>
         </is>
       </c>
     </row>
@@ -1378,77 +1378,77 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>99.3±0.04</t>
+          <t>99.1±0.10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>97.2±0.34</t>
+          <t>99.2±0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>97.8±0.09</t>
+          <t>97.3±1.34</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>99.3±0.04</t>
+          <t>99.1±0.09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.989±0.00062</t>
+          <t>0.984±0.00162</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>93.8±0.33</t>
+          <t>92.6±0.76</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>99.9±0.08</t>
+          <t>98.6±0.36</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>99.9±0.08</t>
+          <t>99.3±0.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.9±0.07</t>
+          <t>98.9±0.27</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>94.1±1.28</t>
+          <t>93.0±0.80</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>94.4±0.38</t>
+          <t>93.2±0.65</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>97.5±0.15</t>
+          <t>98.0±0.21</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>97.0±0.29</t>
+          <t>95.8±0.47</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>97.2±0.19</t>
+          <t>96.9±0.27</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>89.0±2.23</t>
+          <t>86.1±3.65</t>
         </is>
       </c>
     </row>
@@ -1465,77 +1465,77 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>99.6±0.17</t>
+          <t>99.6±0.06</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>98.3±1.08</t>
+          <t>98.5±0.26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>98.6±0.68</t>
+          <t>98.5±0.19</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>99.6±0.17</t>
+          <t>99.6±0.06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.988±0.00534</t>
+          <t>0.987±0.00176</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>93.7±3.26</t>
+          <t>92.7±1.25</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>99.3±1.03</t>
+          <t>99.5±0.43</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>98.9±1.33</t>
+          <t>99.1±0.72</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1±1.11</t>
+          <t>99.3±0.49</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>95.6±2.39</t>
+          <t>95.0±1.14</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>97.2±1.44</t>
+          <t>96.5±0.34</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>99.2±0.40</t>
+          <t>99.2±0.25</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>98.8±0.54</t>
+          <t>98.4±0.22</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>99.0±0.44</t>
+          <t>98.8±0.23</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>95.8±2.45</t>
+          <t>94.2±2.37</t>
         </is>
       </c>
     </row>
@@ -1552,77 +1552,77 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>99.6±0.18</t>
+          <t>99.6±0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>98.1±1.11</t>
+          <t>99.1±0.18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>98.4±0.74</t>
+          <t>98.8±0.45</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>99.6±0.18</t>
+          <t>99.6±0.11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.986±0.00580</t>
+          <t>0.989±0.00364</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>92.7±4.03</t>
+          <t>94.7±1.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>98.6±2.39</t>
+          <t>99.7±0.27</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>98.9±1.16</t>
+          <t>99.2±0.68</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.7±1.71</t>
+          <t>99.4±0.36</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>94.3±3.26</t>
+          <t>96.0±1.00</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>97.2±1.81</t>
+          <t>98.0±0.69</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>99.5±0.26</t>
+          <t>99.4±0.27</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>98.5±1.19</t>
+          <t>99.2±0.45</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>99.0±0.71</t>
+          <t>99.3±0.30</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>90.7±6.40</t>
+          <t>95.6±1.05</t>
         </is>
       </c>
     </row>
@@ -1639,77 +1639,77 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>97.7±0.22</t>
+          <t>97.5±0.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>98.0±0.47</t>
+          <t>97.9±0.54</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>97.7±0.21</t>
+          <t>97.8±0.28</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>97.7±0.22</t>
+          <t>97.5±0.27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.958±0.00403</t>
+          <t>0.958±0.00448</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>84.3±0.77</t>
+          <t>81.2±1.64</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>97.5±0.46</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>99.3±0.13</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>98.4±0.30</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>88.0±1.71</t>
+          <t>89.5±1.70</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>84.3±0.77</t>
+          <t>81.2±1.64</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>95.9±0.43</t>
+          <t>95.3±0.62</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>91.2±0.98</t>
+          <t>90.7±0.53</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>93.5±0.53</t>
+          <t>92.9±0.47</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>84.2±4.64</t>
+          <t>89.5±2.35</t>
         </is>
       </c>
     </row>
@@ -1726,77 +1726,77 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>97.6±0.04</t>
+          <t>97.2±0.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>97.6±0.22</t>
+          <t>97.6±0.19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>97.4±0.09</t>
+          <t>97.5±0.25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>97.6±0.04</t>
+          <t>97.2±0.34</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.956±0.00079</t>
+          <t>0.954±0.00575</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>83.1±0.72</t>
+          <t>79.5±1.85</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>99.9±0.11</t>
+          <t>98.1±0.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>99.7±0.53</t>
+          <t>99.4±0.00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>99.8±0.32</t>
+          <t>98.8±0.00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>88.0±1.88</t>
+          <t>87.8±1.05</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>83.1±0.72</t>
+          <t>79.5±1.85</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>94.3±0.78</t>
+          <t>93.9±0.48</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>90.3±1.27</t>
+          <t>88.6±0.25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>92.2±0.97</t>
+          <t>91.2±0.34</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>84.8±2.95</t>
+          <t>87.6±1.85</t>
         </is>
       </c>
     </row>
@@ -1813,77 +1813,77 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>95.6±0.22</t>
+          <t>96.3±0.14</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>78.0±9.65</t>
+          <t>94.0±0.84</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.7±8.89</t>
+          <t>92.8±0.64</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>95.4±0.27</t>
+          <t>96.3±0.14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.917±0.00415</t>
+          <t>0.930±0.00258</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>74.1±1.15</t>
+          <t>80.5±1.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>83.5±2.35</t>
+          <t>82.6±2.73</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>95.8±2.37</t>
+          <t>95.8±2.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>89.2±1.10</t>
+          <t>88.7±1.90</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>83.8±2.62</t>
+          <t>90.6±0.99</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>74.1±1.20</t>
+          <t>80.6±1.27</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>89.2±1.67</t>
+          <t>93.5±0.34</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>86.4±1.55</t>
+          <t>89.2±0.92</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>87.7±0.78</t>
+          <t>91.3±0.61</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>62.4±8.84</t>
+          <t>80.5±1.66</t>
         </is>
       </c>
     </row>
@@ -1900,77 +1900,77 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>95.6±0.13</t>
+          <t>96.1±0.27</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>72.2±3.05</t>
+          <t>94.0±0.88</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>87.8±7.19</t>
+          <t>93.0±0.98</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>95.3±0.17</t>
+          <t>96.1±0.26</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.916±0.00255</t>
+          <t>0.927±0.00493</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>74.4±1.08</t>
+          <t>79.4±0.57</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>84.2±2.24</t>
+          <t>85.1±2.43</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>94.5±3.52</t>
+          <t>94.2±2.50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>89.0±0.84</t>
+          <t>89.3±1.29</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>82.3±2.47</t>
+          <t>91.3±1.58</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>74.5±1.04</t>
+          <t>79.5±0.47</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>88.2±0.69</t>
+          <t>93.1±0.24</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>87.4±0.90</t>
+          <t>88.7±0.41</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>87.8±0.57</t>
+          <t>90.8±0.23</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>67.1±5.66</t>
+          <t>82.7±3.11</t>
         </is>
       </c>
     </row>
@@ -1987,73 +1987,77 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>98.9±0.09</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>98.2±0.15</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>98.1±0.16</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>98.9±0.09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0.980±0.00172</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>89.5±1.05</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>96.4±1.00</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>89.5±1.05</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>92.6±1.11</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>91.1±0.95</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>91.8±1.03</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>96.4±0.93</t>
         </is>
       </c>
     </row>
@@ -2070,73 +2074,77 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>98.6±0.26</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>97.7±0.40</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>97.6±0.46</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>98.6±0.26</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.975±0.00478</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>84.4±1.78</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>93.6±3.66</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>84.4±1.78</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>88.9±0.76</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>85.8±2.65</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>87.3±1.64</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>93.6±3.77</t>
         </is>
       </c>
     </row>
@@ -2153,77 +2161,77 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>97.0±0.39</t>
+          <t>97.7±0.27</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>90.4±3.06</t>
+          <t>90.5±2.50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>87.9±1.88</t>
+          <t>91.7±0.82</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>97.1±0.38</t>
+          <t>97.7±0.27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.940±0.00796</t>
+          <t>0.954±0.00548</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>73.2±3.36</t>
+          <t>77.3±3.57</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>99.2±0.29</t>
+          <t>100.0±0.04</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>99.1±0.70</t>
+          <t>99.7±0.54</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>99.2±0.34</t>
+          <t>99.9±0.29</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>91.9±1.99</t>
+          <t>93.8±1.51</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>73.3±3.34</t>
+          <t>77.3±3.57</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>90.8±1.36</t>
+          <t>93.9±1.21</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>91.8±0.86</t>
+          <t>94.0±0.83</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>91.3±1.03</t>
+          <t>93.9±0.99</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>75.9±7.26</t>
+          <t>87.0±2.56</t>
         </is>
       </c>
     </row>
@@ -2240,77 +2248,77 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>97.1±0.35</t>
+          <t>97.9±0.14</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>87.1±2.94</t>
+          <t>91.8±1.74</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>87.3±1.91</t>
+          <t>92.1±1.14</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>97.1±0.36</t>
+          <t>97.9±0.13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.940±0.00727</t>
+          <t>0.957±0.00275</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>73.0±3.31</t>
+          <t>77.8±1.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>98.9±0.30</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>99.2±0.59</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>99.1±0.28</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>91.5±1.17</t>
+          <t>94.2±0.80</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>73.1±3.23</t>
+          <t>77.8±1.46</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>90.2±1.02</t>
+          <t>93.6±0.21</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>91.7±1.22</t>
+          <t>94.4±0.48</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>91.0±1.07</t>
+          <t>94.0±0.30</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>71.2±6.34</t>
+          <t>82.8±6.03</t>
         </is>
       </c>
     </row>
@@ -2327,77 +2335,77 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>99.1±0.16</t>
+          <t>98.9±0.21</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>96.7±0.55</t>
+          <t>98.4±0.52</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>96.9±0.52</t>
+          <t>96.0±1.01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>99.1±0.15</t>
+          <t>98.9±0.20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.984±0.00262</t>
+          <t>0.981±0.00359</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>91.9±1.94</t>
+          <t>91.1±1.56</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100.0±0.08</t>
+          <t>98.3±0.65</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>100.0±0.04</t>
+          <t>99.1±0.33</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>100.0±0.06</t>
+          <t>98.7±0.49</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>91.8±1.60</t>
+          <t>91.7±1.31</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>92.7±1.84</t>
+          <t>91.7±1.34</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>96.5±0.88</t>
+          <t>97.2±0.89</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>96.0±1.39</t>
+          <t>95.3±0.75</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>96.2±1.06</t>
+          <t>96.2±0.72</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>84.2±4.17</t>
+          <t>79.9±3.92</t>
         </is>
       </c>
     </row>
@@ -2414,77 +2422,77 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>99.1±0.12</t>
+          <t>98.9±0.14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>95.8±0.36</t>
+          <t>98.7±0.28</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>96.9±0.27</t>
+          <t>97.2±0.72</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>99.1±0.12</t>
+          <t>98.9±0.14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.985±0.00204</t>
+          <t>0.981±0.00243</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>92.6±1.42</t>
+          <t>91.4±1.10</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100.0±0.08</t>
+          <t>98.1±0.77</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>100.0±0.04</t>
+          <t>99.0±0.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>100.0±0.06</t>
+          <t>98.6±0.58</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>92.6±1.14</t>
+          <t>92.9±0.95</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>93.5±1.52</t>
+          <t>92.0±1.04</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>96.9±0.67</t>
+          <t>97.1±0.40</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>96.6±0.92</t>
+          <t>95.2±0.89</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>96.7±0.77</t>
+          <t>96.1±0.60</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>85.8±2.72</t>
+          <t>85.1±4.76</t>
         </is>
       </c>
     </row>
@@ -2501,77 +2509,77 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>99.5±0.22</t>
+          <t>99.6±0.13</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>98.2±0.51</t>
+          <t>98.6±0.43</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>98.2±0.73</t>
+          <t>98.6±0.38</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>99.5±0.22</t>
+          <t>99.6±0.13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.982±0.00698</t>
+          <t>0.986±0.00423</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>89.9±4.46</t>
+          <t>91.7±2.69</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>96.9±2.69</t>
+          <t>98.6±1.43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>98.8±0.87</t>
+          <t>99.1±0.84</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>97.8±1.78</t>
+          <t>98.8±1.11</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>93.2±2.69</t>
+          <t>94.5±1.91</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>93.8±3.53</t>
+          <t>95.0±2.30</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>98.4±0.97</t>
+          <t>98.6±0.63</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>97.1±1.63</t>
+          <t>97.8±1.03</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>97.7±1.29</t>
+          <t>98.2±0.78</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>89.6±6.79</t>
+          <t>90.5±4.57</t>
         </is>
       </c>
     </row>
@@ -2588,77 +2596,77 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>99.6±0.10</t>
+          <t>99.6±0.04</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>98.3±0.25</t>
+          <t>98.5±0.33</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>98.6±0.37</t>
+          <t>98.6±0.16</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>99.6±0.10</t>
+          <t>99.6±0.04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.986±0.00322</t>
+          <t>0.986±0.00153</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>92.0±2.15</t>
+          <t>92.5±0.60</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>99.6±0.35</t>
+          <t>99.0±0.71</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>99.5±0.35</t>
+          <t>99.0±0.70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>99.6±0.28</t>
+          <t>99.0±0.54</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>95.2±1.20</t>
+          <t>94.6±0.72</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>95.0±2.00</t>
+          <t>96.0±0.96</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>98.6±0.26</t>
+          <t>99.1±0.50</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>97.7±1.04</t>
+          <t>98.3±0.42</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>98.1±0.57</t>
+          <t>98.7±0.41</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>92.9±2.52</t>
+          <t>91.1±2.77</t>
         </is>
       </c>
     </row>
@@ -2675,77 +2683,77 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>96.9±0.31</t>
+          <t>96.8±0.44</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>96.2±1.64</t>
+          <t>96.2±1.29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>96.3±0.98</t>
+          <t>96.6±0.68</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>96.9±0.32</t>
+          <t>96.8±0.44</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.943±0.00579</t>
+          <t>0.946±0.00746</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>76.9±5.20</t>
+          <t>73.5±3.94</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>99.9±0.11</t>
+          <t>97.0±0.38</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>99.7±0.53</t>
+          <t>99.1±0.11</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>99.8±0.32</t>
+          <t>98.0±0.25</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>89.0±1.40</t>
+          <t>89.6±1.68</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>76.9±5.20</t>
+          <t>73.6±4.03</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>91.4±1.94</t>
+          <t>91.7±1.32</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>87.9±1.81</t>
+          <t>87.8±1.75</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>89.6±1.87</t>
+          <t>89.7±1.49</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>84.0±2.61</t>
+          <t>90.5±1.84</t>
         </is>
       </c>
     </row>
@@ -2762,77 +2770,77 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>97.0±0.34</t>
+          <t>96.7±0.25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>96.8±0.86</t>
+          <t>96.4±1.14</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>96.6±0.56</t>
+          <t>96.5±0.48</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>97.1±0.36</t>
+          <t>96.7±0.25</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.946±0.00635</t>
+          <t>0.945±0.00417</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>78.9±1.68</t>
+          <t>72.3±3.51</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>97.3±0.42</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>99.0±0.44</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>98.2±0.39</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>87.9±1.71</t>
+          <t>87.9±1.36</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>78.9±1.68</t>
+          <t>72.4±3.52</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>92.2±1.45</t>
+          <t>91.9±1.06</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>88.3±0.96</t>
+          <t>87.3±1.52</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>90.2±1.15</t>
+          <t>89.5±1.28</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>85.7±0.74</t>
+          <t>89.0±1.65</t>
         </is>
       </c>
     </row>
@@ -2849,77 +2857,77 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>94.1±0.38</t>
+          <t>94.7±0.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>71.9±4.55</t>
+          <t>90.3±2.29</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.8±7.82</t>
+          <t>90.9±1.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>93.9±0.39</t>
+          <t>94.7±0.31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.888±0.00730</t>
+          <t>0.901±0.00558</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>65.6±2.31</t>
+          <t>70.4±1.96</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>73.4±3.61</t>
+          <t>74.3±4.84</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>95.9±1.60</t>
+          <t>95.7±0.79</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>83.1±2.34</t>
+          <t>83.6±3.06</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>79.2±3.11</t>
+          <t>86.9±0.62</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>65.7±2.31</t>
+          <t>70.4±2.04</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>85.0±2.08</t>
+          <t>90.0±1.11</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>80.8±2.00</t>
+          <t>83.4±1.26</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>82.9±1.88</t>
+          <t>86.6±1.13</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>57.3±5.06</t>
+          <t>75.0±1.13</t>
         </is>
       </c>
     </row>
@@ -2936,77 +2944,77 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>94.1±0.12</t>
+          <t>95.2±0.41</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>66.2±1.75</t>
+          <t>91.5±1.48</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>85.8±7.62</t>
+          <t>92.4±0.97</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.8±0.13</t>
+          <t>95.1±0.43</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.889±0.00242</t>
+          <t>0.909±0.00788</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>65.4±1.92</t>
+          <t>73.3±1.89</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>74.9±2.52</t>
+          <t>78.1±4.93</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>97.0±0.75</t>
+          <t>95.1±2.23</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>84.5±1.77</t>
+          <t>85.7±3.37</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>76.7±1.53</t>
+          <t>88.0±1.29</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>65.4±1.93</t>
+          <t>73.4±1.83</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>84.6±0.75</t>
+          <t>90.8±0.77</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>81.4±1.28</t>
+          <t>84.7±1.48</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>83.0±0.95</t>
+          <t>87.6±0.99</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>56.8±8.29</t>
+          <t>77.0±1.96</t>
         </is>
       </c>
     </row>
@@ -3023,77 +3031,77 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>98.5±0.32</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>97.3±0.72</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>97.3±0.59</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>98.5±0.33</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.972±0.00594</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>86.3±2.09</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0.000±0.00000</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>92.6±3.07</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>86.3±2.09</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>89.2±4.10</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>86.4±3.29</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>87.8±3.63</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>92.7±3.06</t>
         </is>
       </c>
     </row>
@@ -3110,77 +3118,77 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>98.6±0.11</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>97.7±0.18</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>97.6±0.20</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>98.6±0.11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.975±0.00204</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>86.3±2.90</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0.000±0.00000</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>92.4±2.80</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>86.3±2.90</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>90.2±1.79</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>87.0±2.35</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>88.6±1.99</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>92.4±2.73</t>
         </is>
       </c>
     </row>
@@ -3197,77 +3205,77 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>97.2±0.12</t>
+          <t>98.0±0.22</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>87.9±1.36</t>
+          <t>91.0±1.18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>87.2±1.27</t>
+          <t>91.5±1.19</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>97.2±0.11</t>
+          <t>98.0±0.22</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.943±0.00245</t>
+          <t>0.959±0.00449</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>75.2±1.58</t>
+          <t>81.6±2.32</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>98.9±0.30</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>98.6±0.37</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>98.7±0.18</t>
+          <t>100.0±0.00</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>91.7±0.90</t>
+          <t>94.4±0.71</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>75.3±1.58</t>
+          <t>81.6±2.26</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>92.2±0.86</t>
+          <t>95.2±0.77</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>92.1±0.76</t>
+          <t>94.9±0.52</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>92.1±0.63</t>
+          <t>95.1±0.57</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>89.2±2.66</t>
+          <t>83.3±6.46</t>
         </is>
       </c>
     </row>
@@ -3284,77 +3292,77 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>97.4±0.21</t>
+          <t>98.0±0.15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>86.6±2.92</t>
+          <t>92.3±1.44</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>87.4±1.78</t>
+          <t>92.4±1.29</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>97.4±0.21</t>
+          <t>98.0±0.15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.946±0.00435</t>
+          <t>0.958±0.00304</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>75.5±1.28</t>
+          <t>81.0±2.46</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>98.4±0.62</t>
+          <t>99.4±0.68</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>98.8±0.34</t>
+          <t>100.0±0.04</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>98.6±0.42</t>
+          <t>99.7±0.36</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>92.0±0.66</t>
+          <t>94.0±0.88</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>75.5±1.29</t>
+          <t>81.0±2.46</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>92.6±1.09</t>
+          <t>95.5±1.12</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>91.6±0.64</t>
+          <t>94.6±0.48</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>92.1±0.75</t>
+          <t>95.1±0.69</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>80.8±6.23</t>
+          <t>90.6±2.79</t>
         </is>
       </c>
     </row>
@@ -3371,77 +3379,77 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>99.2±0.06</t>
+          <t>98.9±0.20</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>96.2±0.28</t>
+          <t>98.7±0.32</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>97.1±0.22</t>
+          <t>95.3±0.55</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>99.2±0.06</t>
+          <t>98.9±0.19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.986±0.00102</t>
+          <t>0.981±0.00342</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>92.3±0.70</t>
+          <t>90.4±2.13</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>99.9±0.10</t>
+          <t>98.5±0.44</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>99.9±0.05</t>
+          <t>99.2±0.21</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>99.9±0.07</t>
+          <t>98.8±0.32</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>92.0±1.88</t>
+          <t>90.5±1.79</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>93.1±0.80</t>
+          <t>90.9±1.99</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>97.0±0.52</t>
+          <t>96.4±1.25</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>95.8±0.74</t>
+          <t>94.4±1.64</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>96.4±0.58</t>
+          <t>95.4±1.39</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>84.0±2.98</t>
+          <t>79.2±4.00</t>
         </is>
       </c>
     </row>
@@ -3458,77 +3466,77 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>99.2±0.04</t>
+          <t>99.0±0.14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>96.9±0.53</t>
+          <t>98.9±0.25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>97.2±0.18</t>
+          <t>95.1±1.88</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>99.2±0.04</t>
+          <t>99.0±0.13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.987±0.00076</t>
+          <t>0.982±0.00233</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>92.5±1.05</t>
+          <t>91.3±1.35</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>99.8±0.15</t>
+          <t>98.7±0.15</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>99.9±0.07</t>
+          <t>99.2±0.10</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>99.8±0.11</t>
+          <t>99.0±0.11</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>92.0±1.18</t>
+          <t>91.7±0.83</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>93.2±1.08</t>
+          <t>92.0±1.41</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>97.5±0.25</t>
+          <t>97.1±0.93</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>95.7±0.40</t>
+          <t>95.5±0.69</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>96.6±0.28</t>
+          <t>96.3±0.77</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>85.9±2.28</t>
+          <t>79.1±3.52</t>
         </is>
       </c>
     </row>
@@ -3545,77 +3553,77 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>99.3±0.10</t>
+          <t>99.5±0.18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>97.0±0.98</t>
+          <t>98.5±0.56</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>97.5±0.49</t>
+          <t>98.3±0.47</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>99.3±0.10</t>
+          <t>99.5±0.16</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.978±0.00324</t>
+          <t>0.983±0.00584</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>87.1±2.26</t>
+          <t>90.8±2.72</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>96.8±3.16</t>
+          <t>99.1±1.13</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>98.6±0.77</t>
+          <t>98.7±2.38</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>97.7±1.95</t>
+          <t>98.9±1.61</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>92.5±1.42</t>
+          <t>95.1±1.69</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>91.5±2.57</t>
+          <t>93.1±3.25</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>97.0±1.08</t>
+          <t>98.5±1.21</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>96.0±1.16</t>
+          <t>97.0±1.23</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>96.5±1.08</t>
+          <t>97.8±1.14</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>91.2±6.15</t>
+          <t>89.9±6.88</t>
         </is>
       </c>
     </row>
@@ -3632,77 +3640,77 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>99.5±0.09</t>
+          <t>99.6±0.12</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>98.0±0.14</t>
+          <t>98.7±0.43</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>98.3±0.37</t>
+          <t>98.7±0.22</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>99.5±0.09</t>
+          <t>99.6±0.08</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.983±0.00291</t>
+          <t>0.986±0.00390</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>89.0±4.33</t>
+          <t>90.9±2.69</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>98.3±1.79</t>
+          <t>98.4±0.87</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>97.9±1.32</t>
+          <t>99.2±0.53</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>98.1±1.16</t>
+          <t>98.8±0.39</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>95.3±1.92</t>
+          <t>93.9±1.96</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>89.9±5.01</t>
+          <t>92.8±3.05</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>98.0±1.45</t>
+          <t>98.6±1.01</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>95.7±2.03</t>
+          <t>97.0±1.23</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>96.8±1.70</t>
+          <t>97.8±1.05</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>86.4±7.94</t>
+          <t>87.7±5.27</t>
         </is>
       </c>
     </row>
@@ -3719,77 +3727,77 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>97.3±0.14</t>
+          <t>96.9±0.32</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>96.8±0.33</t>
+          <t>96.3±0.94</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>96.9±0.21</t>
+          <t>96.7±0.62</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>97.3±0.14</t>
+          <t>97.0±0.32</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.950±0.00262</t>
+          <t>0.949±0.00544</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>81.2±1.67</t>
+          <t>74.5±2.41</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>97.5±0.46</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>99.3±0.13</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>98.4±0.30</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>86.4±2.50</t>
+          <t>88.8±1.48</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>81.2±1.67</t>
+          <t>74.5±2.41</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>94.2±0.83</t>
+          <t>92.5±0.87</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>89.3±0.79</t>
+          <t>87.7±1.10</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>91.7±0.76</t>
+          <t>90.1±0.94</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>84.7±1.01</t>
+          <t>88.7±1.46</t>
         </is>
       </c>
     </row>
@@ -3806,77 +3814,77 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>97.2±0.17</t>
+          <t>97.1±0.10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>96.7±0.48</t>
+          <t>96.8±0.90</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>96.7±0.20</t>
+          <t>96.8±0.39</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>97.2±0.16</t>
+          <t>97.1±0.08</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.948±0.00304</t>
+          <t>0.951±0.00172</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>79.5±2.22</t>
+          <t>78.2±1.30</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>96.6±0.46</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>99.0±0.13</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>97.8±0.30</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>86.7±1.36</t>
+          <t>89.6±1.49</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>79.5±2.22</t>
+          <t>78.2±1.30</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>93.8±1.00</t>
+          <t>93.7±0.77</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>89.1±1.07</t>
+          <t>89.0±0.90</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>91.4±0.83</t>
+          <t>91.3±0.81</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>84.2±1.05</t>
+          <t>91.4±1.23</t>
         </is>
       </c>
     </row>
@@ -3893,77 +3901,77 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>94.7±0.18</t>
+          <t>95.4±0.37</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>68.4±3.92</t>
+          <t>91.7±1.24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>79.2±8.90</t>
+          <t>91.1±1.23</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>94.4±0.22</t>
+          <t>95.4±0.37</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.899±0.00346</t>
+          <t>0.913±0.00692</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>68.4±2.66</t>
+          <t>74.6±2.24</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>79.1±4.72</t>
+          <t>78.6±1.92</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>97.8±0.48</t>
+          <t>97.1±1.30</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>87.4±3.11</t>
+          <t>86.9±1.51</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>78.4±4.29</t>
+          <t>88.0±1.96</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>68.6±2.63</t>
+          <t>74.6±2.25</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>86.5±1.82</t>
+          <t>91.2±1.00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>82.0±1.12</t>
+          <t>85.2±1.01</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>84.2±1.24</t>
+          <t>88.1±0.94</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>56.9±9.31</t>
+          <t>76.1±2.77</t>
         </is>
       </c>
     </row>
@@ -3980,77 +3988,77 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>95.2±0.23</t>
+          <t>95.9±0.23</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>68.5±2.99</t>
+          <t>92.3±1.07</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>88.3±6.27</t>
+          <t>92.4±0.57</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>94.9±0.28</t>
+          <t>95.9±0.22</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.908±0.00438</t>
+          <t>0.923±0.00433</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>70.3±0.81</t>
+          <t>75.9±2.32</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>77.5±2.12</t>
+          <t>77.8±2.48</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>97.3±0.68</t>
+          <t>96.6±1.11</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>86.3±1.45</t>
+          <t>86.2±1.19</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>78.5±2.22</t>
+          <t>87.8±1.60</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>70.4±0.78</t>
+          <t>76.1±2.11</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>87.3±0.75</t>
+          <t>92.6±0.51</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>84.0±0.64</t>
+          <t>85.9±1.33</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>85.6±0.58</t>
+          <t>89.1±0.94</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>61.8±2.53</t>
+          <t>75.4±3.27</t>
         </is>
       </c>
     </row>
@@ -4067,73 +4075,77 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>98.9±0.15</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>98.1±0.25</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>98.0±0.26</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>98.9±0.15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.979±0.00272</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>89.4±2.73</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>95.2±3.31</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>89.4±2.73</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>92.9±2.05</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>90.2±2.70</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>91.5±2.10</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>95.2±3.41</t>
         </is>
       </c>
     </row>
@@ -4150,73 +4162,77 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>98.8±0.18</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>98.0±0.34</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>97.9±0.32</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>98.8±0.18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.979±0.00329</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>89.7±2.88</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>100.0±0.00</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>100.0±0.00</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>75.0±0.00</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>91.6±6.37</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>100.0±0.00</t>
+          <t>89.7±2.88</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>92.7±2.58</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>88.9±3.65</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>75.0±0.00</t>
+          <t>90.7±2.93</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.0±0.00</t>
+          <t>91.5±6.48</t>
         </is>
       </c>
     </row>
